--- a/MODELO_FORMULARIO_ENCUESTA.xlsx
+++ b/MODELO_FORMULARIO_ENCUESTA.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -773,6 +773,42 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Pregunta sin sección para asignar durante la importación</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELECCION</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1=Totalmente en desacuerdo;2=En desacuerdo;3=Neutral;4=De acuerdo;5=Totalmente de acuerdo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -784,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -799,9 +835,6 @@
           <t>MOTOR INSTITUCIONAL DE ENCUESTAS - MODELO DE IMPORTACION</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -900,6 +933,20 @@
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SECCION OPCIONAL</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SECCION y SECCION_CODIGO son opcionales. Si quedan vacíos, antes de importar el sistema pedirá asignar una sección existente, crear una nueva o marcar Sin sección.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
